--- a/data/NB-0123-0005_Cat_Loading_Conditions.xlsx
+++ b/data/NB-0123-0005_Cat_Loading_Conditions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tkholiya/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tkholiya/MSSE/Capstone/MERCK-1-26-Team/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7046538C-A79C-8E4A-899F-5F6E64D544AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0EE4DD-DBE2-5640-814B-B8901061C94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{F5FA9269-8A3A-4635-A2B6-9B6C2447D52C}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="27040" windowHeight="15720" xr2:uid="{F5FA9269-8A3A-4635-A2B6-9B6C2447D52C}"/>
   </bookViews>
   <sheets>
     <sheet name="Conditions" sheetId="1" r:id="rId1"/>
@@ -188,9 +188,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,7 +557,7 @@
       <c r="D2">
         <v>0.5</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2">
         <v>0</v>
       </c>
     </row>
@@ -575,8 +574,8 @@
       <c r="D3">
         <v>0.5</v>
       </c>
-      <c r="G3" s="1">
-        <v>5</v>
+      <c r="G3">
+        <v>0.17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -592,8 +591,8 @@
       <c r="D4">
         <v>0.5</v>
       </c>
-      <c r="G4" s="1">
-        <v>10</v>
+      <c r="G4">
+        <v>0.33</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -609,8 +608,8 @@
       <c r="D5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="1">
-        <v>15</v>
+      <c r="G5">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -626,8 +625,8 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="G6" s="1">
-        <v>20</v>
+      <c r="G6">
+        <v>0.75</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -643,8 +642,8 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="G7" s="1">
-        <v>25</v>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -660,8 +659,8 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="G8" s="1">
-        <v>30</v>
+      <c r="G8">
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -677,8 +676,8 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="G9" s="1">
-        <v>35</v>
+      <c r="G9">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -694,8 +693,8 @@
       <c r="D10">
         <v>2</v>
       </c>
-      <c r="G10" s="1">
-        <v>40</v>
+      <c r="G10">
+        <v>2.5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -711,8 +710,8 @@
       <c r="D11">
         <v>2</v>
       </c>
-      <c r="G11" s="1">
-        <v>45</v>
+      <c r="G11">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -728,8 +727,8 @@
       <c r="D12">
         <v>2</v>
       </c>
-      <c r="G12" s="1">
-        <v>50</v>
+      <c r="G12">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -745,8 +744,8 @@
       <c r="D13">
         <v>2</v>
       </c>
-      <c r="G13" s="1">
-        <v>55</v>
+      <c r="G13">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -762,8 +761,8 @@
       <c r="D14">
         <v>4</v>
       </c>
-      <c r="G14" s="1">
-        <v>60</v>
+      <c r="G14">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -779,8 +778,8 @@
       <c r="D15">
         <v>4</v>
       </c>
-      <c r="G15" s="1">
-        <v>65</v>
+      <c r="G15">
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -796,8 +795,8 @@
       <c r="D16">
         <v>4</v>
       </c>
-      <c r="G16" s="1">
-        <v>70</v>
+      <c r="G16">
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -1044,18 +1043,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1197,18 +1196,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE4C9C4F-61EE-45B2-993C-CAF55EFDC531}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{905F9959-3D84-4C2B-9DC0-3DE3B1B96745}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{905F9959-3D84-4C2B-9DC0-3DE3B1B96745}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE4C9C4F-61EE-45B2-993C-CAF55EFDC531}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
